--- a/data/export/2026-10-21-operations.xlsx
+++ b/data/export/2026-10-21-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +820,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +840,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -908,7 +916,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +955,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +966,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1032,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1071,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1082,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1115,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1152,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1176,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1196,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1272,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1322,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1388,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1438,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1504,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1554,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1567,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1615,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1634,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1670,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1731,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1750,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1786,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1847,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1866,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1902,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1963,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1982,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,7 +2007,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2002,35 +2018,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2079,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2098,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2134,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2195,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2214,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2250,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2311,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2330,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2355,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2366,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2427,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2446,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2471,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2482,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2495,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2505,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2543,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2562,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2598,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2626,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2664,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2688,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2708,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2780,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2794,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2830,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2896,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2910,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2946,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3007,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3026,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3062,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-operations.xlsx
+++ b/data/export/2026-10-21-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -726,7 +726,7 @@
       <c r="AC2" s="2" t="inlineStr"/>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -835,14 +835,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>74.0</t>
@@ -850,7 +850,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -883,32 +883,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -916,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -940,17 +944,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -960,13 +964,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -999,32 +1007,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1032,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1056,17 +1068,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1076,13 +1088,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1125,24 +1141,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1152,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1191,22 +1207,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1239,32 +1255,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1272,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1296,33 +1316,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1427,7 +1451,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1438,7 +1462,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1543,7 +1567,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1554,7 +1578,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1644,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1670,7 +1694,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1760,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1775,7 +1799,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1786,7 +1810,7 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1876,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1902,7 +1926,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1992,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2018,7 +2042,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2108,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2134,7 +2158,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2224,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2250,7 +2274,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2340,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2360,13 +2384,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2379,22 +2407,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2432,7 +2460,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2446,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2476,41 +2504,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2543,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2562,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2587,46 +2619,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2659,12 +2695,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2678,7 +2714,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2703,46 +2739,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2775,12 +2815,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2794,7 +2834,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2830,35 +2870,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2891,12 +2931,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2910,7 +2950,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2935,46 +2975,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3007,12 +3051,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3026,7 +3070,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3051,7 +3095,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3062,35 +3106,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3123,12 +3167,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3142,7 +3186,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3167,7 +3211,7 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
@@ -3178,35 +3222,35 @@
       <c r="AC23" s="2" t="inlineStr"/>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3239,12 +3283,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3258,7 +3302,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3283,7 +3327,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3294,7 +3338,7 @@
       <c r="AC24" s="2" t="inlineStr"/>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3307,60 +3351,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3374,7 +3422,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3384,33 +3432,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3423,60 +3475,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3490,7 +3546,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3500,33 +3556,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3539,60 +3599,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3606,7 +3670,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3616,17 +3680,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3636,13 +3700,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3655,22 +3723,22 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3703,12 +3771,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3722,7 +3790,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3747,7 +3815,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3758,7 +3826,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3771,32 +3839,32 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3819,12 +3887,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3832,13 +3900,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3874,7 +3954,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3967,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3897,7 +3977,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3935,12 +4015,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3954,7 +4034,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3990,7 +4070,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4003,7 +4083,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4013,7 +4093,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4051,12 +4131,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4070,7 +4150,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4106,7 +4186,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4119,22 +4199,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4167,12 +4247,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4186,7 +4266,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4222,7 +4302,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4235,22 +4315,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4283,12 +4363,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4302,7 +4382,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4338,7 +4418,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4431,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4361,7 +4441,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4399,12 +4479,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4418,7 +4498,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4454,7 +4534,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4547,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4477,7 +4557,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4515,12 +4595,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4534,7 +4614,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4570,7 +4650,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4663,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4593,7 +4673,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4631,12 +4711,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4650,7 +4730,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4686,7 +4766,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4779,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4709,7 +4789,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4747,12 +4827,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4766,7 +4846,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4802,35 +4882,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4863,12 +4943,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4882,7 +4962,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4907,7 +4987,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4918,35 +4998,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4979,12 +5059,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4998,7 +5078,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5034,35 +5114,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5095,12 +5175,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5114,7 +5194,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5150,35 +5230,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5211,12 +5291,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5230,7 +5310,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5266,35 +5346,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5327,12 +5407,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5346,7 +5426,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5382,35 +5462,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5443,12 +5523,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5462,7 +5542,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5498,35 +5578,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5559,12 +5639,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5578,7 +5658,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5614,35 +5694,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5675,12 +5755,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5694,7 +5774,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5730,35 +5810,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5791,12 +5871,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5810,7 +5890,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5846,35 +5926,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5907,12 +5987,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5926,7 +6006,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5962,35 +6042,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6028,7 +6108,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6042,7 +6122,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6078,35 +6158,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6144,7 +6224,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6158,7 +6238,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6194,35 +6274,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6255,12 +6335,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6274,7 +6354,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6310,35 +6390,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6371,12 +6451,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6390,7 +6470,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6426,35 +6506,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6487,12 +6567,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6506,7 +6586,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6542,35 +6622,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6608,7 +6688,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6622,7 +6702,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6652,13 +6732,3189 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC53" s="2" t="inlineStr"/>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>—/15</t>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:44</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-21-operations.xlsx
+++ b/data/export/2026-10-21-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1495,32 +1495,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1528,7 +1532,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1552,17 +1556,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1572,13 +1576,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1652,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1683,7 +1691,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1760,7 +1768,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1876,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1992,7 +2000,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2108,7 +2116,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2224,7 +2232,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2340,7 +2348,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2460,7 +2468,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2580,7 +2588,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2700,7 +2708,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2936,7 +2944,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2990,7 +2998,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3064,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3172,7 +3180,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3216,13 +3224,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3300,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3345,70 +3357,66 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3422,7 +3430,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3432,17 +3440,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3452,17 +3460,13 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3475,24 +3479,24 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:10</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3505,12 +3509,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
@@ -3532,7 +3536,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3581,7 +3585,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
@@ -3599,7 +3603,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3609,7 +3613,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3619,36 +3623,32 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3680,37 +3680,33 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3723,52 +3719,56 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3800,33 +3800,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3839,32 +3843,32 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq33，推进5站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3892,7 +3896,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3900,25 +3904,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>物理seq26（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>07:49</t>
-        </is>
-      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3943,7 +3935,7 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -3967,7 +3959,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3977,7 +3969,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3987,12 +3979,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4015,12 +4007,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4028,13 +4020,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4083,22 +4087,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4131,12 +4135,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4150,7 +4154,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4199,22 +4203,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4247,12 +4251,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4266,7 +4270,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4315,22 +4319,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4363,7 +4367,7 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4431,7 +4435,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4441,7 +4445,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4479,7 +4483,7 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4498,7 +4502,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4547,22 +4551,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4595,12 +4599,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4663,22 +4667,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4711,12 +4715,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4730,7 +4734,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4779,22 +4783,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4832,7 +4836,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4846,7 +4850,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4895,22 +4899,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4943,12 +4947,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5011,7 +5015,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5021,7 +5025,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5059,12 +5063,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5078,7 +5082,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5127,22 +5131,22 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5175,7 +5179,7 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5194,7 +5198,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5243,22 +5247,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5291,12 +5295,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5359,22 +5363,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5407,7 +5411,7 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5426,7 +5430,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5475,22 +5479,22 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5523,12 +5527,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5591,22 +5595,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5644,7 +5648,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5658,7 +5662,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5707,22 +5711,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5755,12 +5759,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5823,22 +5827,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5871,12 +5875,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5890,7 +5894,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5939,22 +5943,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5987,12 +5991,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6055,7 +6059,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6065,7 +6069,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6103,12 +6107,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6122,7 +6126,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6171,22 +6175,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6219,12 +6223,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6238,7 +6242,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6287,22 +6291,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6340,7 +6344,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6354,7 +6358,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6403,22 +6407,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:35</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6456,7 +6460,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6470,7 +6474,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6519,22 +6523,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6567,12 +6571,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6586,7 +6590,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6635,22 +6639,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6683,12 +6687,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6727,22 +6731,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6755,22 +6755,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -6875,22 +6875,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6985,62 +6985,58 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7048,7 +7044,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7062,7 +7058,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7072,17 +7068,17 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7092,17 +7088,13 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7107,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7125,7 +7117,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7135,32 +7127,36 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7168,7 +7164,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7182,7 +7178,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7192,17 +7188,17 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7212,13 +7208,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7231,59 +7231,55 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7302,7 +7298,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7312,17 +7308,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7332,17 +7328,13 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7355,60 +7347,64 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7432,17 +7428,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7452,13 +7448,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7471,64 +7471,60 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7542,7 +7538,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7552,17 +7548,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7572,17 +7568,13 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -7595,60 +7587,64 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7672,33 +7668,37 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7778,7 +7778,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7827,22 +7827,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7943,22 +7943,22 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8010,7 +8010,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8059,22 +8059,22 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8175,22 +8175,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8242,7 +8242,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8291,7 +8291,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8339,7 +8339,7 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8358,7 +8358,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8407,22 +8407,22 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8455,7 +8455,7 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,22 +8523,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8639,22 +8639,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8687,12 +8687,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8706,7 +8706,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8755,7 +8755,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8765,7 +8765,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8822,7 +8822,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8847,22 +8847,18 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8875,22 +8871,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8923,12 +8919,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8942,7 +8938,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8967,18 +8963,22 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9107,7 +9107,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9155,12 +9155,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9199,22 +9199,18 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9227,22 +9223,22 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -9275,12 +9271,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9294,7 +9290,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9319,18 +9315,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9459,22 +9459,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9507,7 +9507,7 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9556,17 +9556,13 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9579,22 +9575,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9627,7 +9623,7 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9646,7 +9642,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9676,13 +9672,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9695,22 +9695,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9762,7 +9762,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9811,7 +9811,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9859,12 +9859,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9913,6 +9913,122 @@
       </c>
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-21-operations.xlsx
+++ b/data/export/2026-10-21-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -715,18 +715,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -796,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -920,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -959,7 +963,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1044,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1083,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1292,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1346,7 +1350,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1532,7 +1536,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1652,7 +1656,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1768,7 +1772,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1851,32 +1855,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1884,7 +1892,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1908,33 +1916,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1967,32 +1979,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2000,7 +2016,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2024,33 +2040,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2083,32 +2103,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2116,7 +2140,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2140,33 +2164,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2199,32 +2227,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:22</t>
@@ -2232,7 +2264,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2256,33 +2288,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2384,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2387,7 +2423,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2468,7 +2504,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2588,7 +2624,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2627,7 +2663,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2708,7 +2744,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2828,7 +2864,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2944,7 +2980,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2998,7 +3034,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3100,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3180,7 +3216,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3300,7 +3336,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3416,7 +3452,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3473,70 +3509,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3550,7 +3582,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3560,17 +3592,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3585,40 +3617,40 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3651,12 +3683,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3670,7 +3702,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3695,88 +3727,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3790,7 +3822,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3800,65 +3832,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3891,12 +3923,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3910,7 +3942,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3940,51 +3972,55 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq39，推进11站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4007,12 +4043,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4020,25 +4056,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq26（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:49</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4063,46 +4087,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4135,12 +4163,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4154,7 +4182,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4179,18 +4207,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4235,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4213,7 +4245,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4223,32 +4255,36 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4256,7 +4292,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4270,7 +4306,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4280,33 +4316,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4359,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4329,7 +4369,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4339,40 +4379,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4386,7 +4430,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4396,33 +4440,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4435,22 +4483,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4483,12 +4531,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4502,7 +4550,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4527,7 +4575,7 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4551,7 +4599,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4561,7 +4609,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4571,40 +4619,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4618,7 +4670,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4628,33 +4680,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4723,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4677,7 +4733,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4687,12 +4743,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4715,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4728,13 +4784,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:49</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4759,7 +4827,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4783,60 +4851,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4850,7 +4922,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4860,33 +4932,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4899,60 +4975,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4966,7 +5046,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4976,33 +5056,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5015,22 +5099,22 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5063,12 +5147,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5082,7 +5166,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5107,7 +5191,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5131,7 +5215,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5141,7 +5225,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5179,12 +5263,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5198,7 +5282,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5247,22 +5331,22 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5295,12 +5379,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5314,7 +5398,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5363,60 +5447,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5430,7 +5518,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5440,33 +5528,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5479,32 +5571,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq37推进至seq44，推进7站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5527,12 +5619,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5540,13 +5632,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5595,22 +5703,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5643,12 +5751,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5662,7 +5770,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5711,22 +5819,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5759,12 +5867,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5778,7 +5886,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5827,7 +5935,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5837,7 +5945,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5875,12 +5983,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5894,7 +6002,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5943,7 +6051,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -5953,7 +6061,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5991,12 +6099,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6010,7 +6118,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6059,7 +6167,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6069,7 +6177,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6107,12 +6215,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6126,7 +6234,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6175,22 +6283,22 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6223,12 +6331,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6242,7 +6350,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6291,22 +6399,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6339,12 +6447,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6358,7 +6466,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6407,22 +6515,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6455,12 +6563,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6474,7 +6582,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6523,22 +6631,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:40</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6571,12 +6679,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6590,7 +6698,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6639,22 +6747,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6687,12 +6795,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6706,7 +6814,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6755,22 +6863,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6808,7 +6916,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6822,7 +6930,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6847,22 +6955,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>154.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6875,7 +6979,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -6885,7 +6989,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6923,12 +7027,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6942,7 +7046,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6967,7 +7071,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6991,7 +7095,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7001,7 +7105,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7044,7 +7148,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7058,7 +7162,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7083,7 +7187,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7101,62 +7205,58 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7164,7 +7264,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7178,7 +7278,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7188,65 +7288,61 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7284,7 +7380,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7298,7 +7394,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7323,7 +7419,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7334,77 +7430,73 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7418,7 +7510,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7428,65 +7520,61 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7524,7 +7612,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7538,7 +7626,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7568,83 +7656,83 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7658,7 +7746,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7668,17 +7756,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7693,40 +7781,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7759,12 +7847,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7778,7 +7866,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7803,7 +7891,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7814,35 +7902,35 @@
       <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7875,12 +7963,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7894,7 +7982,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7919,7 +8007,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7930,35 +8018,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7991,12 +8079,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8010,7 +8098,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8040,41 +8128,45 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8107,12 +8199,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8126,7 +8218,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8151,46 +8243,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8223,12 +8319,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8242,7 +8338,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8278,35 +8374,35 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8339,12 +8435,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8358,7 +8454,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8383,46 +8479,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8455,12 +8555,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8474,7 +8574,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8499,18 +8599,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -8523,60 +8627,64 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8590,7 +8698,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8600,33 +8708,37 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8751,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8649,7 +8761,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8687,12 +8799,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8706,7 +8818,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8731,7 +8843,7 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
@@ -8755,7 +8867,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8765,7 +8877,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8775,40 +8887,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8822,7 +8938,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8832,33 +8948,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8871,22 +8991,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:05</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8924,7 +9044,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8938,7 +9058,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8963,22 +9083,18 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -8991,60 +9107,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9058,7 +9178,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9068,33 +9188,37 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9107,7 +9231,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9117,7 +9241,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9155,12 +9279,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9174,7 +9298,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9199,7 +9323,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9223,7 +9347,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9233,7 +9357,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9276,7 +9400,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9290,7 +9414,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9320,17 +9444,13 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9463,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9353,7 +9473,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9391,12 +9511,12 @@
       <c r="N76" s="2" t="inlineStr"/>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9410,7 +9530,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9435,7 +9555,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9459,22 +9579,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9507,12 +9627,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9526,7 +9646,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9575,60 +9695,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9642,7 +9766,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9652,17 +9776,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9677,12 +9801,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9695,60 +9819,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>111分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9762,7 +9890,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9772,17 +9900,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9792,13 +9920,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9943,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9821,7 +9953,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9859,12 +9991,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9878,7 +10010,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9927,60 +10059,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9994,41 +10130,2637 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W81" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X81" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y81" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB81" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC81" s="2" t="inlineStr"/>
-      <c r="AD81" s="2" t="inlineStr">
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>111.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-21-operations.xlsx
+++ b/data/export/2026-10-21-operations.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -968,17 +968,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2072,12 +2072,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2444,17 +2444,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5412,17 +5412,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5536,17 +5536,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6404,17 +6404,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7396,12 +7396,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7892,17 +7892,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8760,17 +8760,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10244,17 +10244,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10984,17 +10984,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11312,7 +11312,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11421,12 +11421,12 @@
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -11436,7 +11436,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11523,32 +11523,36 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11556,7 +11560,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11580,17 +11584,17 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
@@ -11600,12 +11604,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11680,7 +11684,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11767,32 +11771,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11800,7 +11808,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11824,17 +11832,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11844,12 +11852,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11887,32 +11895,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11920,7 +11932,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11944,17 +11956,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11964,17 +11976,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12007,32 +12019,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12040,7 +12056,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12064,17 +12080,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12084,17 +12100,17 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -12127,32 +12143,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12160,7 +12180,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12184,17 +12204,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12204,12 +12224,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12280,7 +12300,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12400,7 +12420,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12444,17 +12464,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -12578,7 +12598,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12668,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12692,17 +12712,17 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13164,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13198,7 +13218,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13562,7 +13582,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -13632,7 +13652,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13676,12 +13696,12 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
@@ -13756,7 +13776,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13810,7 +13830,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14090,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14136,7 +14156,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14180,7 +14200,7 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
@@ -14256,7 +14276,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14392,7 +14412,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14446,7 +14466,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14512,7 +14532,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14556,17 +14576,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14780,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14804,17 +14824,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -14880,7 +14900,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14924,17 +14944,17 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15024,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15058,7 +15078,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15148,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15182,7 +15202,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15268,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15292,13 +15312,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC120" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15392,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15422,7 +15446,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15546,7 +15570,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -15612,7 +15636,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15656,17 +15680,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15996,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16016,17 +16040,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16174,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16600,7 +16624,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16654,7 +16678,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16894,7 +16918,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17108,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17138,7 +17162,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17262,7 +17286,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17356,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17376,12 +17400,12 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17452,7 +17476,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17496,7 +17520,7 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
@@ -17576,7 +17600,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17630,7 +17654,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17700,7 +17724,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17744,17 +17768,17 @@
       </c>
       <c r="AB140" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17972,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -17992,17 +18016,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -18068,7 +18092,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18112,17 +18136,17 @@
       </c>
       <c r="AB143" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18216,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18246,7 +18270,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -18316,7 +18340,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18370,7 +18394,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18588,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18618,7 +18642,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18990,7 +19014,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19204,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19494,7 +19518,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -19564,7 +19588,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19812,7 +19836,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19856,17 +19880,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -19936,7 +19960,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -19990,7 +20014,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -20060,7 +20084,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20114,7 +20138,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20362,7 +20386,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20634,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20734,7 +20758,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21072,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21092,12 +21116,12 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
@@ -21300,7 +21324,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21416,7 +21440,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21460,13 +21484,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC170" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC170" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -21536,7 +21564,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21580,17 +21608,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21688,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21704,7 +21732,7 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
@@ -21784,7 +21812,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21908,7 +21936,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -21952,17 +21980,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -22032,7 +22060,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22086,7 +22114,7 @@
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22184,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22200,17 +22228,17 @@
       </c>
       <c r="AB176" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22400,7 +22428,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22454,7 +22482,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22676,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22702,7 +22730,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22826,7 +22854,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22978,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23048,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23074,7 +23102,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -23318,7 +23346,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23416,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23442,7 +23470,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -23719,32 +23747,36 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N189" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N189" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23752,7 +23784,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23776,17 +23808,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23796,17 +23828,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -23839,32 +23871,36 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23872,7 +23908,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23896,17 +23932,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23916,13 +23952,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC190" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC190" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -23955,32 +23995,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23988,7 +24032,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24012,17 +24056,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24032,17 +24076,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -24075,32 +24119,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24108,7 +24156,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24132,17 +24180,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24152,17 +24200,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -24195,32 +24243,36 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N193" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N193" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -24228,7 +24280,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24252,17 +24304,17 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA193" s="2" t="inlineStr">
@@ -24272,12 +24324,12 @@
       </c>
       <c r="AB193" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
@@ -24315,12 +24367,12 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -24348,7 +24400,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24356,10 +24408,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R194" s="2" t="inlineStr"/>
-      <c r="S194" s="2" t="inlineStr"/>
-      <c r="T194" s="2" t="inlineStr"/>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V194" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24402,7 +24470,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -24435,32 +24503,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24468,7 +24540,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24492,17 +24564,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24512,17 +24584,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24555,32 +24627,36 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24588,7 +24664,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24612,17 +24688,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24632,7 +24708,7 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
@@ -24708,7 +24784,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24828,7 +24904,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24882,7 +24958,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24915,32 +24991,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24948,7 +25028,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -24972,17 +25052,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -24992,17 +25072,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -25068,7 +25148,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25122,7 +25202,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -25188,7 +25268,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25242,7 +25322,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -25308,7 +25388,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25362,7 +25442,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25508,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25472,17 +25552,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -25552,7 +25632,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25596,17 +25676,17 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25850,7 +25930,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26040,7 +26120,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26094,7 +26174,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26160,7 +26240,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26520,7 +26600,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26564,17 +26644,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26644,7 +26724,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26688,17 +26768,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26822,7 +26902,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27066,7 +27146,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27390,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27380,7 +27460,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27424,17 +27504,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27558,7 +27638,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -27624,7 +27704,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27668,17 +27748,17 @@
       </c>
       <c r="AB221" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27802,7 +27882,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28120,7 +28200,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28174,7 +28254,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28364,7 +28444,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28732,7 +28812,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28776,17 +28856,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28856,7 +28936,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28900,17 +28980,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29034,7 +29114,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29158,7 +29238,7 @@
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -29406,7 +29486,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29476,7 +29556,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29520,17 +29600,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -29778,7 +29858,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -29844,7 +29924,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29910,7 +29990,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30348,7 +30428,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30404,17 +30484,17 @@
       </c>
       <c r="AB243" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC243" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30534,7 +30614,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30658,7 +30738,7 @@
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30782,7 +30862,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -31154,7 +31234,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -31650,7 +31730,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31774,7 +31854,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31898,7 +31978,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32346,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32584,7 +32664,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32628,17 +32708,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32882,7 +32962,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33006,7 +33086,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -33200,7 +33280,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33378,7 +33458,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -33448,7 +33528,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33492,17 +33572,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33626,7 +33706,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33816,7 +33896,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33870,7 +33950,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33940,7 +34020,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -33984,17 +34064,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34242,7 +34322,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34312,7 +34392,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34356,17 +34436,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34684,7 +34764,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34728,17 +34808,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34978,7 +35058,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35226,7 +35306,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35296,7 +35376,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35470,7 +35550,7 @@
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -35536,7 +35616,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35580,17 +35660,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35710,7 +35790,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35904,7 +35984,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35958,7 +36038,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36028,7 +36108,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36072,17 +36152,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36202,7 +36282,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36520,7 +36600,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36564,17 +36644,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36818,7 +36898,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36888,7 +36968,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -36932,17 +37012,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37190,7 +37270,7 @@
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -37314,7 +37394,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37384,7 +37464,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37508,7 +37588,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37562,7 +37642,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37595,32 +37675,36 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37628,7 +37712,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37652,17 +37736,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37672,17 +37756,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37715,32 +37799,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37748,7 +37836,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37772,17 +37860,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37792,17 +37880,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -37835,32 +37923,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -37868,7 +37960,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -37892,17 +37984,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -37912,17 +38004,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37955,32 +38047,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -37988,7 +38084,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38012,17 +38108,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38032,17 +38128,17 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -38108,7 +38204,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38228,7 +38324,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38272,17 +38368,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38444,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38392,17 +38488,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
